--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122361195</v>
+        <v>122361170</v>
       </c>
       <c r="B2" t="n">
-        <v>97132</v>
+        <v>97371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590379</v>
+        <v>590312</v>
       </c>
       <c r="R2" t="n">
-        <v>6440925</v>
+        <v>6440963</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>några plantor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362753</v>
+        <v>122361726</v>
       </c>
       <c r="B3" t="n">
-        <v>57527</v>
+        <v>78645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,49 +812,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590312</v>
+        <v>590357</v>
       </c>
       <c r="R3" t="n">
-        <v>6440960</v>
+        <v>6441035</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,28 +883,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>torrare barrskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362795</v>
+        <v>122362753</v>
       </c>
       <c r="B4" t="n">
-        <v>94947</v>
+        <v>57527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +919,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590348</v>
+        <v>590312</v>
       </c>
       <c r="R4" t="n">
-        <v>6440992</v>
+        <v>6440960</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +1003,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122361726</v>
+        <v>122362808</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>105280</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,44 +1033,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590357</v>
+        <v>590367</v>
       </c>
       <c r="R5" t="n">
-        <v>6441035</v>
+        <v>6441015</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,30 +1117,25 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>torrare barrskog</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122362808</v>
+        <v>122362785</v>
       </c>
       <c r="B6" t="n">
-        <v>105280</v>
+        <v>98175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,28 +1144,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1175,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590367</v>
+        <v>590332</v>
       </c>
       <c r="R6" t="n">
-        <v>6441015</v>
+        <v>6441025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122362761</v>
+        <v>122362795</v>
       </c>
       <c r="B7" t="n">
-        <v>57744</v>
+        <v>94947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,35 +1263,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1290,13 +1291,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590312</v>
+        <v>590348</v>
       </c>
       <c r="R7" t="n">
-        <v>6440960</v>
+        <v>6440992</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,6 +1335,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1352,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122362785</v>
+        <v>122362761</v>
       </c>
       <c r="B8" t="n">
-        <v>98175</v>
+        <v>57744</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,39 +1366,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1404,13 +1406,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590332</v>
+        <v>590312</v>
       </c>
       <c r="R8" t="n">
-        <v>6441025</v>
+        <v>6440960</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1448,7 +1450,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1467,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122361170</v>
+        <v>122361195</v>
       </c>
       <c r="B9" t="n">
-        <v>97371</v>
+        <v>97132</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,30 +1484,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>569</v>
+        <v>221946</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1515,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590312</v>
+        <v>590379</v>
       </c>
       <c r="R9" t="n">
-        <v>6440963</v>
+        <v>6440925</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,11 +1558,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>några plantor</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1585,6 +1585,365 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122385375</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97371</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>569</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Granbräken</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryopteris cristata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A1773-2025, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>590317</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6440959</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122385387</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97371</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>569</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granbräken</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryopteris cristata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A1773-2025, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>590288</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6441005</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122387490</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57744</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 1773, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>590348</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6440992</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122361170</v>
+        <v>122361195</v>
       </c>
       <c r="B2" t="n">
-        <v>97371</v>
+        <v>97142</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>569</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590312</v>
+        <v>590379</v>
       </c>
       <c r="R2" t="n">
-        <v>6440963</v>
+        <v>6440925</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>några plantor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122361726</v>
+        <v>122361170</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>97381</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,30 +807,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590357</v>
+        <v>590312</v>
       </c>
       <c r="R3" t="n">
-        <v>6441035</v>
+        <v>6440963</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,6 +879,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>några plantor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +898,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>torrare barrskog</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -907,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362753</v>
+        <v>122362795</v>
       </c>
       <c r="B4" t="n">
-        <v>57527</v>
+        <v>94957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,39 +928,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,13 +960,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590312</v>
+        <v>590348</v>
       </c>
       <c r="R4" t="n">
-        <v>6440960</v>
+        <v>6440992</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,6 +1004,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1021,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122362808</v>
+        <v>122362785</v>
       </c>
       <c r="B5" t="n">
-        <v>105280</v>
+        <v>98185</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,28 +1035,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1069,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590367</v>
+        <v>590332</v>
       </c>
       <c r="R5" t="n">
-        <v>6441015</v>
+        <v>6441025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122362785</v>
+        <v>122362808</v>
       </c>
       <c r="B6" t="n">
-        <v>98175</v>
+        <v>105290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,32 +1150,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1184,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590332</v>
+        <v>590367</v>
       </c>
       <c r="R6" t="n">
-        <v>6441025</v>
+        <v>6441015</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122362795</v>
+        <v>122362753</v>
       </c>
       <c r="B7" t="n">
-        <v>94947</v>
+        <v>57527</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,31 +1261,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1291,13 +1301,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590348</v>
+        <v>590312</v>
       </c>
       <c r="R7" t="n">
-        <v>6440992</v>
+        <v>6440960</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,7 +1345,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1354,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122362761</v>
+        <v>122361726</v>
       </c>
       <c r="B8" t="n">
-        <v>57744</v>
+        <v>78646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,53 +1375,44 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590312</v>
+        <v>590357</v>
       </c>
       <c r="R8" t="n">
-        <v>6440960</v>
+        <v>6441035</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,28 +1450,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>torrare barrskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122361195</v>
+        <v>122362761</v>
       </c>
       <c r="B9" t="n">
-        <v>97132</v>
+        <v>57744</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,49 +1490,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590379</v>
+        <v>590312</v>
       </c>
       <c r="R9" t="n">
-        <v>6440925</v>
+        <v>6440960</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,34 +1570,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122385375</v>
+        <v>122385387</v>
       </c>
       <c r="B10" t="n">
-        <v>97371</v>
+        <v>97381</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590317</v>
+        <v>590288</v>
       </c>
       <c r="R10" t="n">
-        <v>6440959</v>
+        <v>6441005</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1676,6 +1676,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385387</v>
+        <v>122385375</v>
       </c>
       <c r="B11" t="n">
-        <v>97371</v>
+        <v>97381</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,7 +1743,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1755,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590288</v>
+        <v>590317</v>
       </c>
       <c r="R11" t="n">
-        <v>6441005</v>
+        <v>6440959</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1791,11 +1796,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122361195</v>
+        <v>122362753</v>
       </c>
       <c r="B2" t="n">
-        <v>97142</v>
+        <v>57527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590379</v>
+        <v>590312</v>
       </c>
       <c r="R2" t="n">
-        <v>6440925</v>
+        <v>6440960</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,34 +771,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122361170</v>
+        <v>122362808</v>
       </c>
       <c r="B3" t="n">
-        <v>97381</v>
+        <v>105290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,42 +805,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>569</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590312</v>
+        <v>590367</v>
       </c>
       <c r="R3" t="n">
-        <v>6440963</v>
+        <v>6441015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,11 +875,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>några plantor</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -896,30 +885,25 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362795</v>
+        <v>122361170</v>
       </c>
       <c r="B4" t="n">
-        <v>94957</v>
+        <v>97381</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,38 +916,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590348</v>
+        <v>590312</v>
       </c>
       <c r="R4" t="n">
-        <v>6440992</v>
+        <v>6440963</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,6 +986,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>några plantor</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,25 +1001,30 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122362785</v>
+        <v>122362761</v>
       </c>
       <c r="B5" t="n">
-        <v>98185</v>
+        <v>57744</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,39 +1033,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1075,13 +1073,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590332</v>
+        <v>590312</v>
       </c>
       <c r="R5" t="n">
-        <v>6441025</v>
+        <v>6440960</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1117,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1138,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122362808</v>
+        <v>122362785</v>
       </c>
       <c r="B6" t="n">
-        <v>105290</v>
+        <v>98185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,28 +1147,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1186,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590367</v>
+        <v>590332</v>
       </c>
       <c r="R6" t="n">
-        <v>6441015</v>
+        <v>6441025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122362753</v>
+        <v>122361195</v>
       </c>
       <c r="B7" t="n">
-        <v>57527</v>
+        <v>97142</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,53 +1262,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590312</v>
+        <v>590379</v>
       </c>
       <c r="R7" t="n">
-        <v>6440960</v>
+        <v>6440925</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,18 +1346,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1474,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122362761</v>
+        <v>122362795</v>
       </c>
       <c r="B9" t="n">
-        <v>57744</v>
+        <v>94957</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,35 +1497,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1526,13 +1525,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590312</v>
+        <v>590348</v>
       </c>
       <c r="R9" t="n">
-        <v>6440960</v>
+        <v>6440992</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,6 +1569,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385375</v>
+        <v>122387490</v>
       </c>
       <c r="B11" t="n">
-        <v>97381</v>
+        <v>57744</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,49 +1724,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>569</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590317</v>
+        <v>590348</v>
       </c>
       <c r="R11" t="n">
-        <v>6440959</v>
+        <v>6440992</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1793,40 +1793,49 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122387490</v>
+        <v>122385375</v>
       </c>
       <c r="B12" t="n">
-        <v>57744</v>
+        <v>97381</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,49 +1848,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590348</v>
+        <v>590317</v>
       </c>
       <c r="R12" t="n">
-        <v>6440992</v>
+        <v>6440959</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1908,39 +1917,30 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122362753</v>
       </c>
       <c r="B2" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362808</v>
+        <v>122361195</v>
       </c>
       <c r="B3" t="n">
-        <v>105290</v>
+        <v>97154</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,27 +805,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -833,14 +837,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590367</v>
+        <v>590379</v>
       </c>
       <c r="R3" t="n">
-        <v>6441015</v>
+        <v>6440925</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,25 +889,30 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122361170</v>
+        <v>122361726</v>
       </c>
       <c r="B4" t="n">
-        <v>97381</v>
+        <v>78651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,35 +921,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>569</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590312</v>
+        <v>590357</v>
       </c>
       <c r="R4" t="n">
-        <v>6440963</v>
+        <v>6441035</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,11 +988,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>några plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +1002,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>torrare barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1024,7 +1023,7 @@
         <v>122362761</v>
       </c>
       <c r="B5" t="n">
-        <v>57744</v>
+        <v>57749</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1135,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122362785</v>
+        <v>122362808</v>
       </c>
       <c r="B6" t="n">
-        <v>98185</v>
+        <v>105303</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,32 +1146,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1187,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590332</v>
+        <v>590367</v>
       </c>
       <c r="R6" t="n">
-        <v>6441025</v>
+        <v>6441015</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122361195</v>
+        <v>122362785</v>
       </c>
       <c r="B7" t="n">
-        <v>97142</v>
+        <v>98197</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,25 +1257,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1290,7 +1285,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1298,14 +1293,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590379</v>
+        <v>590332</v>
       </c>
       <c r="R7" t="n">
-        <v>6440925</v>
+        <v>6441025</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,30 +1345,25 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122361726</v>
+        <v>122362795</v>
       </c>
       <c r="B8" t="n">
-        <v>78646</v>
+        <v>94969</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,44 +1372,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590357</v>
+        <v>590348</v>
       </c>
       <c r="R8" t="n">
-        <v>6441035</v>
+        <v>6440992</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,30 +1452,25 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>torrare barrskog</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122362795</v>
+        <v>122361170</v>
       </c>
       <c r="B9" t="n">
-        <v>94957</v>
+        <v>97393</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,38 +1483,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590348</v>
+        <v>590312</v>
       </c>
       <c r="R9" t="n">
-        <v>6440992</v>
+        <v>6440963</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,6 +1553,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>några plantor</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1573,25 +1568,30 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122385387</v>
+        <v>122385375</v>
       </c>
       <c r="B10" t="n">
-        <v>97381</v>
+        <v>97393</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590288</v>
+        <v>590317</v>
       </c>
       <c r="R10" t="n">
-        <v>6441005</v>
+        <v>6440959</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1676,11 +1676,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,7 +1706,7 @@
         <v>122387490</v>
       </c>
       <c r="B11" t="n">
-        <v>57744</v>
+        <v>57749</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1832,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385375</v>
+        <v>122385387</v>
       </c>
       <c r="B12" t="n">
-        <v>97381</v>
+        <v>97393</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,7 +1862,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1884,10 +1879,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590317</v>
+        <v>590288</v>
       </c>
       <c r="R12" t="n">
-        <v>6440959</v>
+        <v>6441005</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1920,6 +1915,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362753</v>
+        <v>122362808</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
+        <v>105308</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590312</v>
+        <v>590367</v>
       </c>
       <c r="R2" t="n">
-        <v>6440960</v>
+        <v>6441015</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122361195</v>
+        <v>122362761</v>
       </c>
       <c r="B3" t="n">
-        <v>97154</v>
+        <v>57749</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,49 +802,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590379</v>
+        <v>590312</v>
       </c>
       <c r="R3" t="n">
-        <v>6440925</v>
+        <v>6440960</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,34 +882,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122361726</v>
+        <v>122361170</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>97398</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,30 +912,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590357</v>
+        <v>590312</v>
       </c>
       <c r="R4" t="n">
-        <v>6441035</v>
+        <v>6440963</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,6 +984,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>några plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1003,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>torrare barrskog</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1020,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122362761</v>
+        <v>122362753</v>
       </c>
       <c r="B5" t="n">
-        <v>57749</v>
+        <v>57532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,37 +1033,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1134,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122362808</v>
+        <v>122361195</v>
       </c>
       <c r="B6" t="n">
-        <v>105303</v>
+        <v>97159</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,27 +1151,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1178,14 +1183,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590367</v>
+        <v>590379</v>
       </c>
       <c r="R6" t="n">
-        <v>6441015</v>
+        <v>6440925</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,15 +1235,20 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1248,7 +1258,7 @@
         <v>122362785</v>
       </c>
       <c r="B7" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1363,7 +1373,7 @@
         <v>122362795</v>
       </c>
       <c r="B8" t="n">
-        <v>94969</v>
+        <v>94974</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1467,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122361170</v>
+        <v>122361726</v>
       </c>
       <c r="B9" t="n">
-        <v>97393</v>
+        <v>78651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,35 +1489,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>569</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1515,13 +1520,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590312</v>
+        <v>590357</v>
       </c>
       <c r="R9" t="n">
-        <v>6440963</v>
+        <v>6441035</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1551,11 +1556,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>några plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>torrare barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122385375</v>
+        <v>122387490</v>
       </c>
       <c r="B10" t="n">
-        <v>97393</v>
+        <v>57749</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,49 +1604,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>569</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590317</v>
+        <v>590348</v>
       </c>
       <c r="R10" t="n">
-        <v>6440959</v>
+        <v>6440992</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,40 +1673,49 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122387490</v>
+        <v>122385375</v>
       </c>
       <c r="B11" t="n">
-        <v>57749</v>
+        <v>97398</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,49 +1728,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590348</v>
+        <v>590317</v>
       </c>
       <c r="R11" t="n">
-        <v>6440992</v>
+        <v>6440959</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1788,39 +1797,30 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1830,7 +1830,7 @@
         <v>122385387</v>
       </c>
       <c r="B12" t="n">
-        <v>97393</v>
+        <v>97398</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362761</v>
+        <v>122361170</v>
       </c>
       <c r="B3" t="n">
-        <v>57749</v>
+        <v>97398</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,49 +802,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>590312</v>
       </c>
       <c r="R3" t="n">
-        <v>6440960</v>
+        <v>6440963</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,34 +872,45 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>några plantor</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122361170</v>
+        <v>122362761</v>
       </c>
       <c r="B4" t="n">
-        <v>97398</v>
+        <v>57749</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,45 +923,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>569</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>590312</v>
       </c>
       <c r="R4" t="n">
-        <v>6440963</v>
+        <v>6440960</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,35 +997,24 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>några plantor</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122362795</v>
+        <v>122361726</v>
       </c>
       <c r="B8" t="n">
-        <v>94974</v>
+        <v>78651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,45 +1382,44 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590348</v>
+        <v>590357</v>
       </c>
       <c r="R8" t="n">
-        <v>6440992</v>
+        <v>6441035</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,25 +1461,30 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>torrare barrskog</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122361726</v>
+        <v>122362795</v>
       </c>
       <c r="B9" t="n">
-        <v>78651</v>
+        <v>94974</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,44 +1493,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590357</v>
+        <v>590348</v>
       </c>
       <c r="R9" t="n">
-        <v>6441035</v>
+        <v>6440992</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,20 +1573,15 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>torrare barrskog</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362808</v>
+        <v>122362753</v>
       </c>
       <c r="B2" t="n">
-        <v>105308</v>
+        <v>57532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590367</v>
+        <v>590312</v>
       </c>
       <c r="R2" t="n">
-        <v>6441015</v>
+        <v>6440960</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122361170</v>
+        <v>122361195</v>
       </c>
       <c r="B3" t="n">
-        <v>97398</v>
+        <v>97168</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,30 +800,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>569</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granbräken</t>
-        </is>
+        <v>221946</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -834,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590312</v>
+        <v>590379</v>
       </c>
       <c r="R3" t="n">
-        <v>6440963</v>
+        <v>6440925</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,11 +867,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>några plantor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362761</v>
+        <v>122362795</v>
       </c>
       <c r="B4" t="n">
-        <v>57749</v>
+        <v>94983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,35 +915,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>2180</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,13 +938,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590312</v>
+        <v>590348</v>
       </c>
       <c r="R4" t="n">
-        <v>6440960</v>
+        <v>6440992</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,6 +982,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1021,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122362753</v>
+        <v>122362785</v>
       </c>
       <c r="B5" t="n">
-        <v>57532</v>
+        <v>98211</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,39 +1013,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590312</v>
+        <v>590332</v>
       </c>
       <c r="R5" t="n">
-        <v>6440960</v>
+        <v>6441025</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,6 +1092,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1135,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122361195</v>
+        <v>122362808</v>
       </c>
       <c r="B6" t="n">
-        <v>97159</v>
+        <v>105317</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,31 +1127,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
+        <v>221144</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1183,14 +1150,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590379</v>
+        <v>590367</v>
       </c>
       <c r="R6" t="n">
-        <v>6440925</v>
+        <v>6441015</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,30 +1202,25 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122362785</v>
+        <v>122362761</v>
       </c>
       <c r="B7" t="n">
-        <v>98202</v>
+        <v>57749</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,39 +1229,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590332</v>
+        <v>590312</v>
       </c>
       <c r="R7" t="n">
-        <v>6441025</v>
+        <v>6440960</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,7 +1308,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1373,7 +1329,7 @@
         <v>122361726</v>
       </c>
       <c r="B8" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,11 +1343,6 @@
       </c>
       <c r="E8" t="n">
         <v>6425</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1481,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122362795</v>
+        <v>122361170</v>
       </c>
       <c r="B9" t="n">
-        <v>94974</v>
+        <v>97407</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,38 +1448,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
+        <v>569</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590348</v>
+        <v>590312</v>
       </c>
       <c r="R9" t="n">
-        <v>6440992</v>
+        <v>6440963</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,6 +1513,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>några plantor</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1573,25 +1528,30 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122387490</v>
+        <v>122385375</v>
       </c>
       <c r="B10" t="n">
-        <v>57749</v>
+        <v>97407</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,49 +1564,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>569</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590348</v>
+        <v>590317</v>
       </c>
       <c r="R10" t="n">
-        <v>6440992</v>
+        <v>6440959</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,49 +1628,40 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385375</v>
+        <v>122387490</v>
       </c>
       <c r="B11" t="n">
-        <v>97398</v>
+        <v>57749</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,49 +1674,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>569</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Granbräken</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590317</v>
+        <v>590348</v>
       </c>
       <c r="R11" t="n">
-        <v>6440959</v>
+        <v>6440992</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,30 +1738,39 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1830,7 +1780,7 @@
         <v>122385387</v>
       </c>
       <c r="B12" t="n">
-        <v>97398</v>
+        <v>97407</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,11 +1794,6 @@
       </c>
       <c r="E12" t="n">
         <v>569</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Granbräken</t>
-        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362753</v>
+        <v>122362761</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
+        <v>57753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -784,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122361195</v>
+        <v>122362795</v>
       </c>
       <c r="B3" t="n">
-        <v>97168</v>
+        <v>94996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,41 +805,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>2180</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590379</v>
+        <v>590348</v>
       </c>
       <c r="R3" t="n">
-        <v>6440925</v>
+        <v>6440992</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,30 +881,25 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362795</v>
+        <v>122361170</v>
       </c>
       <c r="B4" t="n">
-        <v>94983</v>
+        <v>97420</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,33 +912,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>569</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granbräken</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590348</v>
+        <v>590312</v>
       </c>
       <c r="R4" t="n">
-        <v>6440992</v>
+        <v>6440963</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,6 +982,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>några plantor</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -986,25 +997,30 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122362785</v>
+        <v>122362808</v>
       </c>
       <c r="B5" t="n">
-        <v>98211</v>
+        <v>105330</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,27 +1029,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1048,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590332</v>
+        <v>590367</v>
       </c>
       <c r="R5" t="n">
-        <v>6441025</v>
+        <v>6441015</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122362808</v>
+        <v>122361195</v>
       </c>
       <c r="B6" t="n">
-        <v>105317</v>
+        <v>97181</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,22 +1144,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>221946</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1150,14 +1176,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590367</v>
+        <v>590379</v>
       </c>
       <c r="R6" t="n">
-        <v>6441015</v>
+        <v>6440925</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,25 +1228,30 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122362761</v>
+        <v>122362753</v>
       </c>
       <c r="B7" t="n">
-        <v>57749</v>
+        <v>57536</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,32 +1260,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1326,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122361726</v>
+        <v>122362785</v>
       </c>
       <c r="B8" t="n">
-        <v>78652</v>
+        <v>98224</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,39 +1374,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590357</v>
+        <v>590332</v>
       </c>
       <c r="R8" t="n">
-        <v>6441035</v>
+        <v>6441025</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,30 +1462,25 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>torrare barrskog</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122361170</v>
+        <v>122361726</v>
       </c>
       <c r="B9" t="n">
-        <v>97407</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,30 +1489,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>569</v>
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1475,13 +1520,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590312</v>
+        <v>590357</v>
       </c>
       <c r="R9" t="n">
-        <v>6440963</v>
+        <v>6441035</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,11 +1556,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>några plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,7 +1570,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>sumpskog</t>
+          <t>torrare barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1551,7 +1591,7 @@
         <v>122385375</v>
       </c>
       <c r="B10" t="n">
-        <v>97407</v>
+        <v>97420</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,6 +1605,11 @@
       </c>
       <c r="E10" t="n">
         <v>569</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Granbräken</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1658,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122387490</v>
+        <v>122385387</v>
       </c>
       <c r="B11" t="n">
-        <v>57749</v>
+        <v>97420</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,44 +1719,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>569</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granbräken</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590348</v>
+        <v>590288</v>
       </c>
       <c r="R11" t="n">
-        <v>6440992</v>
+        <v>6441005</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,19 +1788,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,28 +1804,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385387</v>
+        <v>122387490</v>
       </c>
       <c r="B12" t="n">
-        <v>97407</v>
+        <v>57753</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1793,44 +1839,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>569</v>
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590288</v>
+        <v>590348</v>
       </c>
       <c r="R12" t="n">
-        <v>6441005</v>
+        <v>6440992</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,14 +1908,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,19 +1929,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362761</v>
+        <v>122362795</v>
       </c>
       <c r="B2" t="n">
-        <v>57753</v>
+        <v>95009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590312</v>
+        <v>590348</v>
       </c>
       <c r="R2" t="n">
-        <v>6440960</v>
+        <v>6440992</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362795</v>
+        <v>122361170</v>
       </c>
       <c r="B3" t="n">
-        <v>94996</v>
+        <v>97433</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,38 +798,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590348</v>
+        <v>590312</v>
       </c>
       <c r="R3" t="n">
-        <v>6440992</v>
+        <v>6440963</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,6 +868,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>några plantor</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -881,25 +883,30 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122361170</v>
+        <v>122362753</v>
       </c>
       <c r="B4" t="n">
-        <v>97420</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,49 +915,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>569</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>590312</v>
       </c>
       <c r="R4" t="n">
-        <v>6440963</v>
+        <v>6440960</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,45 +993,34 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>några plantor</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122362808</v>
+        <v>122362785</v>
       </c>
       <c r="B5" t="n">
-        <v>105330</v>
+        <v>98237</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,28 +1029,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1065,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590367</v>
+        <v>590332</v>
       </c>
       <c r="R5" t="n">
-        <v>6441015</v>
+        <v>6441025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122361195</v>
+        <v>122362761</v>
       </c>
       <c r="B6" t="n">
-        <v>97181</v>
+        <v>57753</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,49 +1148,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590379</v>
+        <v>590312</v>
       </c>
       <c r="R6" t="n">
-        <v>6440925</v>
+        <v>6440960</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,34 +1228,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122362753</v>
+        <v>122361195</v>
       </c>
       <c r="B7" t="n">
-        <v>57536</v>
+        <v>97194</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,53 +1258,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590312</v>
+        <v>590379</v>
       </c>
       <c r="R7" t="n">
-        <v>6440960</v>
+        <v>6440925</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,28 +1342,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122362785</v>
+        <v>122362808</v>
       </c>
       <c r="B8" t="n">
-        <v>98224</v>
+        <v>105343</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,32 +1378,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590332</v>
+        <v>590367</v>
       </c>
       <c r="R8" t="n">
-        <v>6441025</v>
+        <v>6441015</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122385375</v>
+        <v>122385387</v>
       </c>
       <c r="B10" t="n">
-        <v>97420</v>
+        <v>97433</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590317</v>
+        <v>590288</v>
       </c>
       <c r="R10" t="n">
-        <v>6440959</v>
+        <v>6441005</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1676,6 +1676,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385387</v>
+        <v>122385375</v>
       </c>
       <c r="B11" t="n">
-        <v>97420</v>
+        <v>97433</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,7 +1743,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1755,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590288</v>
+        <v>590317</v>
       </c>
       <c r="R11" t="n">
-        <v>6441005</v>
+        <v>6440959</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1791,11 +1796,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362795</v>
+        <v>122361726</v>
       </c>
       <c r="B2" t="n">
-        <v>95009</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590348</v>
+        <v>590357</v>
       </c>
       <c r="R2" t="n">
-        <v>6440992</v>
+        <v>6441035</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,15 +766,20 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>torrare barrskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -903,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362753</v>
+        <v>122362808</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>105343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +919,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590312</v>
+        <v>590367</v>
       </c>
       <c r="R4" t="n">
-        <v>6440960</v>
+        <v>6441015</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,6 +999,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1132,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122362761</v>
+        <v>122361195</v>
       </c>
       <c r="B6" t="n">
-        <v>57753</v>
+        <v>97194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,49 +1149,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590312</v>
+        <v>590379</v>
       </c>
       <c r="R6" t="n">
-        <v>6440960</v>
+        <v>6440925</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,28 +1229,34 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122361195</v>
+        <v>122362753</v>
       </c>
       <c r="B7" t="n">
-        <v>97194</v>
+        <v>57536</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,53 +1265,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590379</v>
+        <v>590312</v>
       </c>
       <c r="R7" t="n">
-        <v>6440925</v>
+        <v>6440960</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,34 +1349,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122362808</v>
+        <v>122362761</v>
       </c>
       <c r="B8" t="n">
-        <v>105343</v>
+        <v>57753</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,31 +1383,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1414,13 +1419,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590367</v>
+        <v>590312</v>
       </c>
       <c r="R8" t="n">
-        <v>6441015</v>
+        <v>6440960</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1463,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1477,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122361726</v>
+        <v>122362795</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>95009</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,44 +1493,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590357</v>
+        <v>590348</v>
       </c>
       <c r="R9" t="n">
-        <v>6441035</v>
+        <v>6440992</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,30 +1573,25 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>torrare barrskog</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122385387</v>
+        <v>122387490</v>
       </c>
       <c r="B10" t="n">
-        <v>97433</v>
+        <v>57753</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,49 +1604,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>569</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590288</v>
+        <v>590348</v>
       </c>
       <c r="R10" t="n">
-        <v>6441005</v>
+        <v>6440992</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,14 +1673,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,26 +1694,25 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385375</v>
+        <v>122385387</v>
       </c>
       <c r="B11" t="n">
         <v>97433</v>
@@ -1743,7 +1747,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1760,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590317</v>
+        <v>590288</v>
       </c>
       <c r="R11" t="n">
-        <v>6440959</v>
+        <v>6441005</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1796,6 +1800,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1832,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122387490</v>
+        <v>122385375</v>
       </c>
       <c r="B12" t="n">
-        <v>57753</v>
+        <v>97433</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,49 +1848,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590348</v>
+        <v>590317</v>
       </c>
       <c r="R12" t="n">
-        <v>6440992</v>
+        <v>6440959</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1908,39 +1917,30 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122361726</v>
+        <v>122361170</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>97436</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590357</v>
+        <v>590312</v>
       </c>
       <c r="R2" t="n">
-        <v>6441035</v>
+        <v>6440963</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>några plantor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +778,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>torrare barrskog</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122361170</v>
+        <v>122362753</v>
       </c>
       <c r="B3" t="n">
-        <v>97433</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,49 +808,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>569</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>590312</v>
       </c>
       <c r="R3" t="n">
-        <v>6440963</v>
+        <v>6440960</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,45 +886,34 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>några plantor</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362808</v>
+        <v>122362761</v>
       </c>
       <c r="B4" t="n">
-        <v>105343</v>
+        <v>57753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,31 +926,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590367</v>
+        <v>590312</v>
       </c>
       <c r="R4" t="n">
-        <v>6441015</v>
+        <v>6440960</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +1006,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122362785</v>
+        <v>122361726</v>
       </c>
       <c r="B5" t="n">
-        <v>98237</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,53 +1036,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590332</v>
+        <v>590357</v>
       </c>
       <c r="R5" t="n">
-        <v>6441025</v>
+        <v>6441035</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,25 +1115,30 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>torrare barrskog</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122361195</v>
+        <v>122362795</v>
       </c>
       <c r="B6" t="n">
-        <v>97194</v>
+        <v>95011</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,46 +1151,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590379</v>
+        <v>590348</v>
       </c>
       <c r="R6" t="n">
-        <v>6440925</v>
+        <v>6440992</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,30 +1227,25 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122362753</v>
+        <v>122362785</v>
       </c>
       <c r="B7" t="n">
-        <v>57536</v>
+        <v>98240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,39 +1254,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1305,13 +1294,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590312</v>
+        <v>590332</v>
       </c>
       <c r="R7" t="n">
-        <v>6440960</v>
+        <v>6441025</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,6 +1338,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1367,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122362761</v>
+        <v>122361195</v>
       </c>
       <c r="B8" t="n">
-        <v>57753</v>
+        <v>97197</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,49 +1373,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590312</v>
+        <v>590379</v>
       </c>
       <c r="R8" t="n">
-        <v>6440960</v>
+        <v>6440925</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,28 +1453,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122362795</v>
+        <v>122362808</v>
       </c>
       <c r="B9" t="n">
-        <v>95009</v>
+        <v>105346</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,25 +1493,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590348</v>
+        <v>590367</v>
       </c>
       <c r="R9" t="n">
-        <v>6440992</v>
+        <v>6441015</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122387490</v>
+        <v>122385387</v>
       </c>
       <c r="B10" t="n">
-        <v>57753</v>
+        <v>97436</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,49 +1604,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590348</v>
+        <v>590288</v>
       </c>
       <c r="R10" t="n">
-        <v>6440992</v>
+        <v>6441005</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,19 +1673,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,28 +1689,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385387</v>
+        <v>122385375</v>
       </c>
       <c r="B11" t="n">
-        <v>97433</v>
+        <v>97436</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,7 +1743,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1764,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590288</v>
+        <v>590317</v>
       </c>
       <c r="R11" t="n">
-        <v>6441005</v>
+        <v>6440959</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,11 +1796,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385375</v>
+        <v>122387490</v>
       </c>
       <c r="B12" t="n">
-        <v>97433</v>
+        <v>57753</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,49 +1839,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>569</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590317</v>
+        <v>590348</v>
       </c>
       <c r="R12" t="n">
-        <v>6440959</v>
+        <v>6440992</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1917,30 +1908,39 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122361170</v>
+        <v>122361195</v>
       </c>
       <c r="B2" t="n">
-        <v>97436</v>
+        <v>97197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>569</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590312</v>
+        <v>590379</v>
       </c>
       <c r="R2" t="n">
-        <v>6440963</v>
+        <v>6440925</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>några plantor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362753</v>
+        <v>122362761</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>57753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +807,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -910,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362761</v>
+        <v>122361170</v>
       </c>
       <c r="B4" t="n">
-        <v>57753</v>
+        <v>97436</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,49 +925,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>590312</v>
       </c>
       <c r="R4" t="n">
-        <v>6440960</v>
+        <v>6440963</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,34 +995,45 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>några plantor</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122361726</v>
+        <v>122362808</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>105346</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,44 +1042,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590357</v>
+        <v>590367</v>
       </c>
       <c r="R5" t="n">
-        <v>6441035</v>
+        <v>6441015</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,20 +1126,15 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>torrare barrskog</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1357,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122361195</v>
+        <v>122362753</v>
       </c>
       <c r="B8" t="n">
-        <v>97197</v>
+        <v>57536</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,53 +1375,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590379</v>
+        <v>590312</v>
       </c>
       <c r="R8" t="n">
-        <v>6440925</v>
+        <v>6440960</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,34 +1459,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122362808</v>
+        <v>122361726</v>
       </c>
       <c r="B9" t="n">
-        <v>105346</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,49 +1489,44 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590367</v>
+        <v>590357</v>
       </c>
       <c r="R9" t="n">
-        <v>6441015</v>
+        <v>6441035</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,22 +1568,27 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>torrare barrskog</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122385387</v>
+        <v>122385375</v>
       </c>
       <c r="B10" t="n">
         <v>97436</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590288</v>
+        <v>590317</v>
       </c>
       <c r="R10" t="n">
-        <v>6441005</v>
+        <v>6440959</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1676,11 +1676,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385375</v>
+        <v>122387490</v>
       </c>
       <c r="B11" t="n">
-        <v>97436</v>
+        <v>57753</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,49 +1719,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>569</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590317</v>
+        <v>590348</v>
       </c>
       <c r="R11" t="n">
-        <v>6440959</v>
+        <v>6440992</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1793,40 +1788,49 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122387490</v>
+        <v>122385387</v>
       </c>
       <c r="B12" t="n">
-        <v>57753</v>
+        <v>97436</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,49 +1843,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590348</v>
+        <v>590288</v>
       </c>
       <c r="R12" t="n">
-        <v>6440992</v>
+        <v>6441005</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1908,19 +1912,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,18 +1928,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122361195</v>
+        <v>122362785</v>
       </c>
       <c r="B2" t="n">
-        <v>97197</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -723,14 +723,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590379</v>
+        <v>590332</v>
       </c>
       <c r="R2" t="n">
-        <v>6440925</v>
+        <v>6441025</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,30 +775,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362761</v>
+        <v>122362795</v>
       </c>
       <c r="B3" t="n">
-        <v>57753</v>
+        <v>95012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,35 +806,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590312</v>
+        <v>590348</v>
       </c>
       <c r="R3" t="n">
-        <v>6440960</v>
+        <v>6440992</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122361170</v>
+        <v>122362761</v>
       </c>
       <c r="B4" t="n">
-        <v>97436</v>
+        <v>57754</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,45 +913,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>569</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>590312</v>
       </c>
       <c r="R4" t="n">
-        <v>6440963</v>
+        <v>6440960</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,45 +987,34 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>några plantor</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122362808</v>
+        <v>122362753</v>
       </c>
       <c r="B5" t="n">
-        <v>105346</v>
+        <v>57537</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,35 +1023,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590367</v>
+        <v>590312</v>
       </c>
       <c r="R5" t="n">
-        <v>6441015</v>
+        <v>6440960</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1107,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122362795</v>
+        <v>122362808</v>
       </c>
       <c r="B6" t="n">
-        <v>95011</v>
+        <v>105347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,25 +1141,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1185,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590348</v>
+        <v>590367</v>
       </c>
       <c r="R6" t="n">
-        <v>6440992</v>
+        <v>6441015</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122362785</v>
+        <v>122361170</v>
       </c>
       <c r="B7" t="n">
-        <v>98240</v>
+        <v>97437</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,50 +1248,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590332</v>
+        <v>590312</v>
       </c>
       <c r="R7" t="n">
-        <v>6441025</v>
+        <v>6440963</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,6 +1322,11 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>några plantor</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1348,25 +1337,30 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122362753</v>
+        <v>122361726</v>
       </c>
       <c r="B8" t="n">
-        <v>57536</v>
+        <v>78657</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,49 +1373,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590312</v>
+        <v>590357</v>
       </c>
       <c r="R8" t="n">
-        <v>6440960</v>
+        <v>6441035</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,28 +1444,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>torrare barrskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122361726</v>
+        <v>122361195</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>97198</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,30 +1480,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221946</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590357</v>
+        <v>590379</v>
       </c>
       <c r="R9" t="n">
-        <v>6441035</v>
+        <v>6440925</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>torrare barrskog</t>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122385375</v>
+        <v>122387490</v>
       </c>
       <c r="B10" t="n">
-        <v>97436</v>
+        <v>57754</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,49 +1604,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>569</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590317</v>
+        <v>590348</v>
       </c>
       <c r="R10" t="n">
-        <v>6440959</v>
+        <v>6440992</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,40 +1673,49 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122387490</v>
+        <v>122385387</v>
       </c>
       <c r="B11" t="n">
-        <v>57753</v>
+        <v>97437</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,49 +1728,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590348</v>
+        <v>590288</v>
       </c>
       <c r="R11" t="n">
-        <v>6440992</v>
+        <v>6441005</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1788,19 +1797,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,28 +1813,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385387</v>
+        <v>122385375</v>
       </c>
       <c r="B12" t="n">
-        <v>97436</v>
+        <v>97437</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,7 +1867,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1879,10 +1884,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590288</v>
+        <v>590317</v>
       </c>
       <c r="R12" t="n">
-        <v>6441005</v>
+        <v>6440959</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1915,11 +1920,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362785</v>
+        <v>122361195</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>97201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -723,14 +723,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590332</v>
+        <v>590379</v>
       </c>
       <c r="R2" t="n">
-        <v>6441025</v>
+        <v>6440925</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,25 +775,30 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362795</v>
+        <v>122362785</v>
       </c>
       <c r="B3" t="n">
-        <v>95012</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,29 +807,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -834,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590348</v>
+        <v>590332</v>
       </c>
       <c r="R3" t="n">
-        <v>6440992</v>
+        <v>6441025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362761</v>
+        <v>122362753</v>
       </c>
       <c r="B4" t="n">
-        <v>57754</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,37 +922,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1011,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122362753</v>
+        <v>122361170</v>
       </c>
       <c r="B5" t="n">
-        <v>57537</v>
+        <v>97440</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,53 +1036,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>590312</v>
       </c>
       <c r="R5" t="n">
-        <v>6440960</v>
+        <v>6440963</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,34 +1110,45 @@
           <t>2025-01-28</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>några plantor</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122362808</v>
+        <v>122362761</v>
       </c>
       <c r="B6" t="n">
-        <v>105347</v>
+        <v>57754</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,31 +1161,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,13 +1197,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590367</v>
+        <v>590312</v>
       </c>
       <c r="R6" t="n">
-        <v>6441015</v>
+        <v>6440960</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,7 +1241,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122361170</v>
+        <v>122362808</v>
       </c>
       <c r="B7" t="n">
-        <v>97437</v>
+        <v>105350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,42 +1275,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>569</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590312</v>
+        <v>590367</v>
       </c>
       <c r="R7" t="n">
-        <v>6440963</v>
+        <v>6441015</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,11 +1345,6 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>några plantor</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1337,20 +1355,15 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1360,7 +1373,7 @@
         <v>122361726</v>
       </c>
       <c r="B8" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1468,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122361195</v>
+        <v>122362795</v>
       </c>
       <c r="B9" t="n">
-        <v>97198</v>
+        <v>95015</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,46 +1497,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590379</v>
+        <v>590348</v>
       </c>
       <c r="R9" t="n">
-        <v>6440925</v>
+        <v>6440992</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,30 +1573,25 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122387490</v>
+        <v>122385387</v>
       </c>
       <c r="B10" t="n">
-        <v>57754</v>
+        <v>97440</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,49 +1604,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590348</v>
+        <v>590288</v>
       </c>
       <c r="R10" t="n">
-        <v>6440992</v>
+        <v>6441005</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,19 +1673,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,28 +1689,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385387</v>
+        <v>122387490</v>
       </c>
       <c r="B11" t="n">
-        <v>97437</v>
+        <v>57754</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,49 +1724,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>569</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590288</v>
+        <v>590348</v>
       </c>
       <c r="R11" t="n">
-        <v>6441005</v>
+        <v>6440992</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,14 +1793,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,19 +1814,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1835,7 +1835,7 @@
         <v>122385375</v>
       </c>
       <c r="B12" t="n">
-        <v>97437</v>
+        <v>97440</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122361195</v>
+        <v>122361170</v>
       </c>
       <c r="B2" t="n">
-        <v>97201</v>
+        <v>97440</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590379</v>
+        <v>590312</v>
       </c>
       <c r="R2" t="n">
-        <v>6440925</v>
+        <v>6440963</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>några plantor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362785</v>
+        <v>122362761</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>57754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,39 +808,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,13 +848,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590332</v>
+        <v>590312</v>
       </c>
       <c r="R3" t="n">
-        <v>6441025</v>
+        <v>6440960</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,7 +892,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362753</v>
+        <v>122361726</v>
       </c>
       <c r="B4" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,49 +926,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590312</v>
+        <v>590357</v>
       </c>
       <c r="R4" t="n">
-        <v>6440960</v>
+        <v>6441035</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,28 +997,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>torrare barrskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122361170</v>
+        <v>122362753</v>
       </c>
       <c r="B5" t="n">
-        <v>97440</v>
+        <v>57537</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,49 +1033,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>569</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>590312</v>
       </c>
       <c r="R5" t="n">
-        <v>6440963</v>
+        <v>6440960</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,45 +1111,34 @@
           <t>2025-01-28</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>några plantor</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122362761</v>
+        <v>122362808</v>
       </c>
       <c r="B6" t="n">
-        <v>57754</v>
+        <v>105350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,35 +1151,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1197,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590312</v>
+        <v>590367</v>
       </c>
       <c r="R6" t="n">
-        <v>6440960</v>
+        <v>6441015</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,6 +1227,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1259,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122362808</v>
+        <v>122362785</v>
       </c>
       <c r="B7" t="n">
-        <v>105350</v>
+        <v>98244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,28 +1258,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1307,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590367</v>
+        <v>590332</v>
       </c>
       <c r="R7" t="n">
-        <v>6441015</v>
+        <v>6441025</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122361726</v>
+        <v>122362795</v>
       </c>
       <c r="B8" t="n">
-        <v>78660</v>
+        <v>95015</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,44 +1373,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590357</v>
+        <v>590348</v>
       </c>
       <c r="R8" t="n">
-        <v>6441035</v>
+        <v>6440992</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,30 +1453,25 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>torrare barrskog</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122362795</v>
+        <v>122361195</v>
       </c>
       <c r="B9" t="n">
-        <v>95015</v>
+        <v>97201</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,38 +1484,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>221946</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590348</v>
+        <v>590379</v>
       </c>
       <c r="R9" t="n">
-        <v>6440992</v>
+        <v>6440925</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,22 +1568,27 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122385387</v>
+        <v>122385375</v>
       </c>
       <c r="B10" t="n">
         <v>97440</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590288</v>
+        <v>590317</v>
       </c>
       <c r="R10" t="n">
-        <v>6441005</v>
+        <v>6440959</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1676,11 +1676,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1832,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385375</v>
+        <v>122385387</v>
       </c>
       <c r="B12" t="n">
         <v>97440</v>
@@ -1867,7 +1862,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1884,10 +1879,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590317</v>
+        <v>590288</v>
       </c>
       <c r="R12" t="n">
-        <v>6440959</v>
+        <v>6441005</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1920,6 +1915,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362761</v>
+        <v>122361726</v>
       </c>
       <c r="B3" t="n">
-        <v>57754</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,53 +808,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590312</v>
+        <v>590357</v>
       </c>
       <c r="R3" t="n">
-        <v>6440960</v>
+        <v>6441035</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,28 +883,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>torrare barrskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122361726</v>
+        <v>122362761</v>
       </c>
       <c r="B4" t="n">
-        <v>78660</v>
+        <v>57754</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,44 +919,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590357</v>
+        <v>590312</v>
       </c>
       <c r="R4" t="n">
-        <v>6441035</v>
+        <v>6440960</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,24 +1003,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>torrare barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1825,126 +1825,6 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>122385387</v>
-      </c>
-      <c r="B12" t="n">
-        <v>97440</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>569</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Granbräken</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Dryopteris cristata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>A1773-2025, Sm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>590288</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6441005</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Ukna</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Stefan Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1773-2025 artfynd.xlsx
+++ b/artfynd/A 1773-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>122361170</v>
       </c>
       <c r="B2" t="n">
-        <v>97440</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,42 +791,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122361726</v>
+        <v>122385375</v>
       </c>
       <c r="B3" t="n">
-        <v>78660</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590357</v>
+        <v>590317</v>
       </c>
       <c r="R3" t="n">
-        <v>6441035</v>
+        <v>6440959</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,12 +868,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,11 +885,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>torrare barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -907,15 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122362761</v>
+        <v>122385387</v>
       </c>
       <c r="B4" t="n">
-        <v>57754</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,49 +912,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590312</v>
+        <v>590288</v>
       </c>
       <c r="R4" t="n">
-        <v>6440960</v>
+        <v>6441005</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,12 +978,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,33 +997,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122362753</v>
+        <v>122387506</v>
       </c>
       <c r="B5" t="n">
-        <v>57537</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,35 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590312</v>
+        <v>590290</v>
       </c>
       <c r="R5" t="n">
-        <v>6440960</v>
+        <v>6440974</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1103,12 +1092,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,6 +1116,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1135,15 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122362808</v>
+        <v>122362795</v>
       </c>
       <c r="B6" t="n">
-        <v>105350</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,29 +1146,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1183,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590367</v>
+        <v>590348</v>
       </c>
       <c r="R6" t="n">
-        <v>6441015</v>
+        <v>6440992</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,15 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122362785</v>
+        <v>122361726</v>
       </c>
       <c r="B7" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,49 +1248,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 1773, Svartgöl, Sm</t>
+          <t>A1773-2025, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590332</v>
+        <v>590357</v>
       </c>
       <c r="R7" t="n">
-        <v>6441025</v>
+        <v>6441035</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,30 +1323,30 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>torrare barrskog</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122362795</v>
+        <v>122362761</v>
       </c>
       <c r="B8" t="n">
-        <v>95015</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,27 +1354,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1405,13 +1390,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590348</v>
+        <v>590312</v>
       </c>
       <c r="R8" t="n">
-        <v>6440992</v>
+        <v>6440960</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1449,7 +1434,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1468,15 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122361195</v>
+        <v>122387490</v>
       </c>
       <c r="B9" t="n">
-        <v>97201</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,46 +1463,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590379</v>
+        <v>590348</v>
       </c>
       <c r="R9" t="n">
-        <v>6440925</v>
+        <v>6440992</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,12 +1529,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,89 +1553,78 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122385375</v>
+        <v>122362753</v>
       </c>
       <c r="B10" t="n">
-        <v>97440</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>569</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A1773-2025, Sm</t>
+          <t>A 1773, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590317</v>
+        <v>590312</v>
       </c>
       <c r="R10" t="n">
-        <v>6440959</v>
+        <v>6440960</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,12 +1648,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,70 +1662,64 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122387490</v>
+        <v>122362785</v>
       </c>
       <c r="B11" t="n">
-        <v>57754</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1755,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590348</v>
+        <v>590332</v>
       </c>
       <c r="R11" t="n">
-        <v>6440992</v>
+        <v>6441025</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,22 +1757,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:45</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:45</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,6 +1771,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1824,6 +1787,337 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122436260</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öndal-Svartgöl_A A 1764-2025, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>590274</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6441004</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122362808</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 1773, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>590367</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6441015</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122361195</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A1773-2025, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>590379</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6440925</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
